--- a/assets/constructions/examples/ctd_mcr.xlsx
+++ b/assets/constructions/examples/ctd_mcr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,67 +659,82 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DQ1306002W WP15PE</t>
+          <t>9166140800</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>HELION</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DQ13</t>
+          <t>91.6614</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>KSH</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>h11</t>
-        </is>
-      </c>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>HB-6</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -728,25 +743,17 @@
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>WP15PE</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>Volcano</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DIN 6527</t>
+          <t>HELION NORM</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -756,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -768,11 +775,11 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr"/>
@@ -785,7 +792,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2020/End Mills Widia Hanita RU</t>
+          <t>2023/HELION_general_catalog</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -798,64 +805,87 @@
       </c>
       <c r="AT2" t="b">
         <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>9089.48</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R.B42.120C040.SA</t>
+          <t>GYF95180</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BRICE</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RB42</t>
+          <t>GYF95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>e8</t>
+          <t>js12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
-        <v>11.2</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="M3" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -869,11 +899,15 @@
           <t>h6</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>PM60</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>AlCrN</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -884,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB3" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -896,11 +930,11 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
@@ -913,35 +947,54 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2022/BRICE</t>
+          <t>2018 - YG1 - OnlyOne</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>PME</t>
         </is>
       </c>
       <c r="AS3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
         <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>7818.96</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>PKH</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R.A32.080R020.SP</t>
+          <t>ECR-B3 08-12/27W08R02A63 IC08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BRICE</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RA32</t>
+          <t>ECR-B3-R</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -950,40 +1003,34 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>e8</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HB-8</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -992,12 +1039,12 @@
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>IC08</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
@@ -1015,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="AB4" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
@@ -1024,11 +1071,11 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
@@ -1041,7 +1088,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2022/BRICE</t>
+          <t>2019/rotation-toos-2019-milling-tools.pdf</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1053,13 +1100,24 @@
         <v>0</v>
       </c>
       <c r="AT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>767016006LT TIALN-LT</t>
+          <t>DQ1316006W WP15PE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,22 +1127,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>DQ13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PMKS</t>
+          <t>KSH</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>e8</t>
+          <t>h11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -1093,29 +1151,29 @@
         <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>15.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1131,16 +1189,20 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>TIAlN-LT</t>
+          <t>WP15PE</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>AlTiN</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>DIN 6527</t>
+        </is>
+      </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
@@ -1151,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="AB5" t="n">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
@@ -1160,11 +1222,11 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr"/>
@@ -1177,7 +1239,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2017/WIDIA Master Catalog</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1190,12 +1252,23 @@
       </c>
       <c r="AT5" t="b">
         <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R.B42.200C040.SA</t>
+          <t>R.B41.060R010.SA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1205,7 +1278,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RB42</t>
+          <t>RB41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1222,32 +1295,32 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>19.2</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1276,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1319,6 +1392,25 @@
       <c r="AT6" t="b">
         <v>1</v>
       </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4230.11</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>4230.11</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
